--- a/resource-mapping/Endocrine_Resource_Mapping.xlsx
+++ b/resource-mapping/Endocrine_Resource_Mapping.xlsx
@@ -527,7 +527,7 @@
     <row r="1" ht="34.5" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>Endocrine Block — 3rd Party Resource Mapping</t>
+          <t>Endocrine Block — 3rd Party Resource Mapping · v1.0 (2026-04-21)</t>
         </is>
       </c>
     </row>
